--- a/data/trans_camb/P6905-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P6905-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 28,16</t>
+          <t>-16,93; 29,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,62; 11,98</t>
+          <t>-31,44; 10,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,26; 27,17</t>
+          <t>-27,27; 28,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 31,21</t>
+          <t>-21,08; 30,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-37,96; 9,85</t>
+          <t>-35,7; 13,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,71; 11,35</t>
+          <t>-41,98; 12,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 24,01</t>
+          <t>-11,32; 21,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,17; 4,82</t>
+          <t>-28,46; 5,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 13,75</t>
+          <t>-26,21; 15,19</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,27; 96,14</t>
+          <t>-32,7; 99,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-56,44; 38,83</t>
+          <t>-57,97; 37,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-61,66; 93,78</t>
+          <t>-53,16; 93,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-26,74; 65,08</t>
+          <t>-28,47; 67,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,05; 18,89</t>
+          <t>-49,26; 26,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,7; 21,84</t>
+          <t>-56,29; 24,18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,94; 59,57</t>
+          <t>-18,88; 51,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,22; 13,81</t>
+          <t>-47,02; 13,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,12; 32,95</t>
+          <t>-45,4; 38,01</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 22,41</t>
+          <t>-11,93; 21,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 21,98</t>
+          <t>-6,96; 23,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-21,81; 15,66</t>
+          <t>-19,93; 18,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-25,62; 15,72</t>
+          <t>-26,54; 14,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 36,69</t>
+          <t>-3,64; 37,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,66; 49,98</t>
+          <t>7,57; 49,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 14,85</t>
+          <t>-10,96; 14,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 23,7</t>
+          <t>-1,5; 22,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 27,61</t>
+          <t>-0,13; 26,42</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,21; 151,16</t>
+          <t>-36,24; 145,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,76; 145,58</t>
+          <t>-21,92; 154,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-75,91; 105,08</t>
+          <t>-70,67; 129,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-70,03; 102,03</t>
+          <t>-72,12; 90,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 237,64</t>
+          <t>-12,09; 256,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,58; 350,11</t>
+          <t>16,84; 327,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 81,29</t>
+          <t>-36,05; 78,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 132,43</t>
+          <t>-5,64; 122,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 152,64</t>
+          <t>-3,06; 146,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 25,69</t>
+          <t>-19,85; 26,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-32,45; 10,59</t>
+          <t>-32,36; 8,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-39,69; -6,92</t>
+          <t>-38,86; -6,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 32,22</t>
+          <t>-18,05; 32,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,27; 23,51</t>
+          <t>-24,92; 21,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 17,23</t>
+          <t>-21,4; 17,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 21,83</t>
+          <t>-14,07; 20,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 7,36</t>
+          <t>-25,37; 6,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 1,13</t>
+          <t>-25,52; 0,31</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 186,11</t>
+          <t>-59,71; 185,1</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-88,07; 100,7</t>
+          <t>-89,39; 71,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -21,5</t>
+          <t>-100,0; -17,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-76,68; 528,45</t>
+          <t>-78,36; 497,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,06; 277,59</t>
+          <t>-61,81; 362,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,93; 157,43</t>
+          <t>-49,72; 156,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,12; 79,01</t>
+          <t>-84,55; 50,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-77,81; 12,82</t>
+          <t>-77,39; 3,72</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 9,9</t>
+          <t>-23,67; 11,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 38,32</t>
+          <t>-5,57; 38,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 37,73</t>
+          <t>-6,08; 39,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 44,18</t>
+          <t>-13,89; 41,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 49,25</t>
+          <t>-7,93; 45,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-43,47; 17,93</t>
+          <t>-37,48; 17,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 18,33</t>
+          <t>-10,26; 18,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 37,02</t>
+          <t>2,93; 34,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 21,23</t>
+          <t>-20,54; 19,8</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-75,16; 61,58</t>
+          <t>-72,1; 82,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,29; 232,42</t>
+          <t>-24,13; 218,47</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-39,33; 230,24</t>
+          <t>-22,62; 251,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 306,6</t>
+          <t>-29,52; 247,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 297,16</t>
+          <t>-16,77; 302,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-77,02; 71,74</t>
+          <t>-78,45; 70,46</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-34,58; 99,56</t>
+          <t>-30,22; 96,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,5; 191,87</t>
+          <t>7,72; 172,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,51; 94,91</t>
+          <t>-57,38; 86,91</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-29,76; 24,28</t>
+          <t>-31,04; 22,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,58; 51,41</t>
+          <t>-9,63; 50,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 10,97</t>
+          <t>-31,6; 10,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-36,07; 54,55</t>
+          <t>-37,01; 61,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-36,77; 58,13</t>
+          <t>-37,83; 58,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-80,54; -2,56</t>
+          <t>-80,35; -2,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 31,36</t>
+          <t>-16,77; 32,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 48,3</t>
+          <t>-7,78; 47,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-37,32; 1,63</t>
+          <t>-36,52; 2,25</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 216,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,52; 460,27</t>
+          <t>-43,36; 419,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-86,7; 134,67</t>
+          <t>-85,05; 119,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-46,25; 218,01</t>
+          <t>-45,62; 260,59</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-49,6; 491,16</t>
+          <t>-49,99; 364,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-94,82; 45,25</t>
+          <t>-96,02; -0,14</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-45,12; 169,83</t>
+          <t>-42,28; 171,17</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 270,82</t>
+          <t>-21,67; 240,34</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-83,54; 22,8</t>
+          <t>-80,96; 20,89</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-44,63; -2,07</t>
+          <t>-44,19; -2,6</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-52,03; -8,57</t>
+          <t>-53,93; -9,65</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-47,19; -4,97</t>
+          <t>-47,32; -6,77</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-72,42; -5,77</t>
+          <t>-67,18; -0,27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 29,61</t>
+          <t>-65,26; 29,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-66,45; -8,95</t>
+          <t>-64,49; -6,24</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-45,27; -10,73</t>
+          <t>-45,82; -11,71</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-48,55; -6,72</t>
+          <t>-48,02; -7,72</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-45,41; -12,05</t>
+          <t>-43,7; -11,08</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-77,02; -1,66</t>
+          <t>-75,86; -2,19</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-92,4; -18,12</t>
+          <t>-93,45; -22,76</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-82,29; -12,27</t>
+          <t>-81,87; -13,08</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-90,9; -10,62</t>
+          <t>-89,28; 0,37</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-80,76; 61,88</t>
+          <t>-83,8; 63,42</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-80,54; -24,39</t>
+          <t>-78,5; -15,47</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-76,62; -24,18</t>
+          <t>-74,92; -23,54</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-83,34; -13,44</t>
+          <t>-82,47; -15,44</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-73,97; -27,48</t>
+          <t>-73,05; -27,56</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-21,03; 11,19</t>
+          <t>-20,0; 12,73</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-29,19; -2,51</t>
+          <t>-30,53; -1,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 8,52</t>
+          <t>-22,44; 6,94</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 24,62</t>
+          <t>-18,93; 23,94</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-23,5; 17,21</t>
+          <t>-24,63; 17,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 18,6</t>
+          <t>-19,59; 18,02</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-13,41; 12,19</t>
+          <t>-12,58; 13,74</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-21,31; 1,64</t>
+          <t>-20,01; 2,31</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 7,55</t>
+          <t>-13,48; 8,38</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-55,36; 43,58</t>
+          <t>-53,17; 51,59</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-73,07; -7,26</t>
+          <t>-74,71; -1,06</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 36,14</t>
+          <t>-57,46; 28,01</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 86,36</t>
+          <t>-39,36; 80,93</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-45,56; 62,1</t>
+          <t>-47,98; 62,07</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 69,71</t>
+          <t>-36,73; 66,28</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-32,32; 43,71</t>
+          <t>-31,71; 49,95</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-51,98; 6,37</t>
+          <t>-50,29; 8,84</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-36,72; 26,92</t>
+          <t>-32,59; 28,08</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-25,1; -0,36</t>
+          <t>-24,41; 1,62</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 18,72</t>
+          <t>-16,12; 16,76</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 13,0</t>
+          <t>-15,07; 12,71</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 18,3</t>
+          <t>-29,9; 21,08</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-44,81; 1,02</t>
+          <t>-43,46; 1,79</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-32,96; 10,23</t>
+          <t>-32,48; 8,65</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 3,25</t>
+          <t>-22,75; 4,85</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 6,52</t>
+          <t>-20,67; 6,2</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 6,94</t>
+          <t>-15,18; 9,49</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-80,69; 5,21</t>
+          <t>-80,42; 15,95</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-48,07; 83,06</t>
+          <t>-54,1; 78,11</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-50,71; 62,15</t>
+          <t>-49,21; 60,38</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-59,56; 50,06</t>
+          <t>-59,7; 62,47</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-89,01; 5,15</t>
+          <t>-89,69; 7,21</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-64,79; 39,85</t>
+          <t>-67,01; 33,02</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-62,08; 11,96</t>
+          <t>-64,03; 17,99</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-60,46; 23,89</t>
+          <t>-59,6; 24,68</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-47,1; 27,95</t>
+          <t>-44,34; 36,55</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 2,25</t>
+          <t>-9,85; 2,63</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 3,71</t>
+          <t>-9,14; 4,05</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-13,92; -0,03</t>
+          <t>-13,78; -0,2</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 10,02</t>
+          <t>-9,5; 9,37</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 9,98</t>
+          <t>-9,64; 9,53</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-19,64; -0,22</t>
+          <t>-19,53; 0,2</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 4,73</t>
+          <t>-6,75; 3,8</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 3,86</t>
+          <t>-6,1; 4,9</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-11,82; -1,23</t>
+          <t>-11,74; -0,66</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-32,03; 9,38</t>
+          <t>-30,45; 10,02</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-27,52; 13,67</t>
+          <t>-28,7; 15,23</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 0,23</t>
+          <t>-41,48; -0,59</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 27,22</t>
+          <t>-21,26; 25,63</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 27,17</t>
+          <t>-20,72; 26,01</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-44,15; -1,26</t>
+          <t>-43,83; 0,0</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 15,97</t>
+          <t>-18,98; 11,39</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 12,36</t>
+          <t>-16,91; 15,67</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-32,56; -3,69</t>
+          <t>-32,19; -2,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6905-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P6905-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-11,46</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-16,4</t>
+          <t>-21,62</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-6,91</t>
+          <t>-15,74</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,93; 29,11</t>
+          <t>-16,32; 27,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-31,44; 10,27</t>
+          <t>-32,28; 11,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,27; 28,61</t>
+          <t>-33,67; 12,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 30,94</t>
+          <t>-22,73; 27,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 13,96</t>
+          <t>-35,86; 10,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,98; 12,26</t>
+          <t>-44,83; 4,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 21,83</t>
+          <t>-10,21; 23,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,46; 5,57</t>
+          <t>-26,94; 4,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-26,21; 15,19</t>
+          <t>-32,05; 4,05</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-1,23%</t>
+          <t>-26,98%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-25,58%</t>
+          <t>-33,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-13,51%</t>
+          <t>-30,78%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 99,71</t>
+          <t>-30,3; 89,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-57,97; 37,12</t>
+          <t>-58,6; 43,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,16; 93,93</t>
+          <t>-67,76; 42,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 67,91</t>
+          <t>-29,83; 56,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,26; 26,83</t>
+          <t>-48,91; 20,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,29; 24,18</t>
+          <t>-61,35; 7,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 51,32</t>
+          <t>-17,49; 57,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,02; 13,4</t>
+          <t>-45,45; 11,04</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,4; 38,01</t>
+          <t>-55,89; 10,61</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-4,28</t>
+          <t>-0,38</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,65</t>
+          <t>27,73</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,02</t>
+          <t>13,94</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 21,57</t>
+          <t>-10,3; 24,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 23,16</t>
+          <t>-7,84; 22,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,93; 18,11</t>
+          <t>-17,45; 21,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,54; 14,95</t>
+          <t>-26,56; 14,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 37,66</t>
+          <t>-5,62; 37,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 49,01</t>
+          <t>9,23; 47,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 14,01</t>
+          <t>-11,38; 14,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 22,4</t>
+          <t>-1,21; 23,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 26,42</t>
+          <t>0,56; 29,28</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-18,0%</t>
+          <t>-1,6%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>112,15%</t>
+          <t>104,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>56,66%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 145,9</t>
+          <t>-33,17; 163,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 154,45</t>
+          <t>-23,87; 165,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-70,67; 129,26</t>
+          <t>-59,18; 148,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,12; 90,65</t>
+          <t>-73,16; 109,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 256,94</t>
+          <t>-18,33; 252,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,84; 327,17</t>
+          <t>20,62; 319,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,05; 78,18</t>
+          <t>-36,31; 77,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 122,52</t>
+          <t>-3,44; 138,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 146,6</t>
+          <t>0,37; 166,52</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-21,51</t>
+          <t>-21,7</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-11,38</t>
+          <t>-11,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 26,07</t>
+          <t>-20,76; 26,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 8,08</t>
+          <t>-34,52; 6,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-38,86; -6,39</t>
+          <t>-39,39; -6,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 32,26</t>
+          <t>-20,94; 30,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 21,89</t>
+          <t>-28,89; 20,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 17,62</t>
+          <t>-21,35; 16,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 20,29</t>
+          <t>-14,24; 18,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 6,62</t>
+          <t>-25,48; 6,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-25,52; 0,31</t>
+          <t>-24,81; 0,08</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-84,28%</t>
+          <t>-85,05%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-49,78%</t>
+          <t>-50,5%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-59,71; 185,1</t>
+          <t>-58,49; 193,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-89,39; 71,22</t>
+          <t>-100,0; 65,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -17,33</t>
+          <t>-100,0; -17,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-78,36; 497,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 330,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-61,81; 362,64</t>
+          <t>-63,96; 286,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-49,72; 156,36</t>
+          <t>-50,96; 130,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-84,55; 50,18</t>
+          <t>-84,61; 52,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-77,39; 3,72</t>
+          <t>-75,84; 2,78</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14,68</t>
+          <t>24,58</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-7,38</t>
+          <t>10,59</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>19,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-23,67; 11,02</t>
+          <t>-24,14; 9,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 38,54</t>
+          <t>-5,45; 37,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 39,13</t>
+          <t>0,63; 45,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 41,13</t>
+          <t>-13,45; 41,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 45,23</t>
+          <t>-5,68; 47,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-37,48; 17,5</t>
+          <t>-15,29; 30,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 18,11</t>
+          <t>-13,13; 18,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,93; 34,79</t>
+          <t>3,93; 36,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-20,54; 19,8</t>
+          <t>3,26; 32,66</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-22,98%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-72,1; 82,73</t>
+          <t>-75,71; 64,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,13; 218,47</t>
+          <t>-21,22; 236,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 251,87</t>
+          <t>-0,23; 278,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-29,52; 247,96</t>
+          <t>-30,44; 223,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 302,21</t>
+          <t>-14,97; 289,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-78,45; 70,46</t>
+          <t>-31,45; 192,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-30,22; 96,39</t>
+          <t>-39,9; 90,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,72; 172,32</t>
+          <t>9,75; 180,59</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-57,38; 86,91</t>
+          <t>9,96; 182,36</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-9,08</t>
+          <t>-10,52</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-42,96</t>
+          <t>-44,88</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-17,12</t>
+          <t>-18,76</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-31,04; 22,44</t>
+          <t>-29,34; 22,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 50,41</t>
+          <t>-12,66; 52,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-31,6; 10,44</t>
+          <t>-32,32; 8,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 61,18</t>
+          <t>-35,99; 58,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-37,83; 58,08</t>
+          <t>-38,23; 58,14</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-80,35; -2,55</t>
+          <t>-81,97; -4,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 32,35</t>
+          <t>-19,78; 33,37</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 47,34</t>
+          <t>-10,82; 45,35</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-36,52; 2,25</t>
+          <t>-40,03; -1,78</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-38,52%</t>
+          <t>-44,66%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-76,16%</t>
+          <t>-79,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-54,86%</t>
+          <t>-60,09%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 216,55</t>
+          <t>-100,0; 236,55</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-43,36; 419,36</t>
+          <t>-44,1; 530,88</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-85,05; 119,53</t>
+          <t>-87,8; 96,19</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,62; 260,59</t>
+          <t>-46,11; 322,68</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-49,99; 364,17</t>
+          <t>-52,48; 266,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-96,02; -0,14</t>
+          <t>-96,43; 4,58</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-42,28; 171,17</t>
+          <t>-48,94; 179,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 240,34</t>
+          <t>-25,98; 231,34</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-80,96; 20,89</t>
+          <t>-84,83; 5,76</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-27,02</t>
+          <t>-28,22</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-39,74</t>
+          <t>-40,44</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-28,92</t>
+          <t>-29,92</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-44,19; -2,6</t>
+          <t>-44,88; -5,2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-53,93; -9,65</t>
+          <t>-52,7; -10,22</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-47,32; -6,77</t>
+          <t>-48,13; -7,62</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-67,18; -0,27</t>
+          <t>-68,72; -6,04</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-65,26; 29,46</t>
+          <t>-62,51; 29,23</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-64,49; -6,24</t>
+          <t>-64,06; -9,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-45,82; -11,71</t>
+          <t>-45,24; -9,88</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-48,02; -7,72</t>
+          <t>-49,42; -7,02</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-43,7; -11,08</t>
+          <t>-45,45; -14,04</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-57,66%</t>
+          <t>-60,22%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-61,06%</t>
+          <t>-62,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-56,21%</t>
+          <t>-58,15%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-75,86; -2,19</t>
+          <t>-77,75; -11,69</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-93,45; -22,76</t>
+          <t>-91,9; -21,31</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-81,87; -13,08</t>
+          <t>-82,56; -19,15</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-89,28; 0,37</t>
+          <t>-90,88; -12,91</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-83,8; 63,42</t>
+          <t>-81,9; 63,49</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-78,5; -15,47</t>
+          <t>-79,19; -24,68</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-74,92; -23,54</t>
+          <t>-76,38; -21,96</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-82,47; -15,44</t>
+          <t>-84,84; -14,17</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-73,05; -27,56</t>
+          <t>-75,55; -31,57</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-8,1</t>
+          <t>-5,95</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>-0,78</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,97</t>
+          <t>-2,37</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-20,0; 12,73</t>
+          <t>-21,5; 11,93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-30,53; -1,49</t>
+          <t>-30,6; -2,93</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 6,94</t>
+          <t>-21,44; 8,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 23,94</t>
+          <t>-17,81; 25,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-24,63; 17,36</t>
+          <t>-22,9; 16,94</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 18,02</t>
+          <t>-18,22; 17,86</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 13,74</t>
+          <t>-12,81; 13,21</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 2,31</t>
+          <t>-21,42; 0,69</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 8,38</t>
+          <t>-13,82; 8,35</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-24,76%</t>
+          <t>-18,19%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>-1,97%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-8,5%</t>
+          <t>-6,79%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-53,17; 51,59</t>
+          <t>-54,94; 45,97</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-74,71; -1,06</t>
+          <t>-75,99; -11,32</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-57,46; 28,01</t>
+          <t>-52,83; 33,16</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 80,93</t>
+          <t>-35,75; 92,22</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-47,98; 62,07</t>
+          <t>-44,86; 57,73</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-36,73; 66,28</t>
+          <t>-35,9; 69,15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 49,95</t>
+          <t>-31,74; 44,45</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-50,29; 8,84</t>
+          <t>-52,83; 4,35</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-32,59; 28,08</t>
+          <t>-33,2; 30,17</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,36</t>
+          <t>-0,63</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-15,22</t>
+          <t>-23,02</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-5,66</t>
+          <t>-8,46</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-24,41; 1,62</t>
+          <t>-24,36; -0,02</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 16,76</t>
+          <t>-15,59; 16,61</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 12,71</t>
+          <t>-14,45; 14,8</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-29,9; 21,08</t>
+          <t>-31,04; 16,47</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 1,79</t>
+          <t>-42,46; -0,24</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 8,65</t>
+          <t>-38,89; -4,09</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 4,85</t>
+          <t>-20,6; 4,07</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 6,2</t>
+          <t>-21,31; 6,02</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-15,18; 9,49</t>
+          <t>-18,06; 2,15</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-8,98%</t>
+          <t>-2,39%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-35,16%</t>
+          <t>-53,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-17,91%</t>
+          <t>-26,76%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-80,42; 15,95</t>
+          <t>-79,58; 5,72</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-54,1; 78,11</t>
+          <t>-50,91; 78,91</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-49,21; 60,38</t>
+          <t>-47,81; 70,71</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-59,7; 62,47</t>
+          <t>-63,38; 47,19</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-89,69; 7,21</t>
+          <t>-86,84; 15,31</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-67,01; 33,02</t>
+          <t>-74,5; -8,77</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-64,03; 17,99</t>
+          <t>-59,48; 15,77</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-59,6; 24,68</t>
+          <t>-58,65; 23,36</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-44,34; 36,55</t>
+          <t>-52,05; 8,63</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-7,2</t>
+          <t>-4,81</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-8,66</t>
+          <t>-7,38</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-5,84</t>
+          <t>-4,34</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 2,63</t>
+          <t>-10,93; 2,39</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 4,05</t>
+          <t>-9,49; 3,3</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-13,78; -0,2</t>
+          <t>-11,83; 2,18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 9,37</t>
+          <t>-10,16; 9,7</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 9,53</t>
+          <t>-7,8; 11,88</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 0,2</t>
+          <t>-15,28; 1,32</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 3,8</t>
+          <t>-7,24; 4,38</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 4,9</t>
+          <t>-6,47; 3,96</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-11,74; -0,66</t>
+          <t>-8,89; 0,72</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-23,97%</t>
+          <t>-16,02%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-21,15%</t>
+          <t>-18,02%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-17,44%</t>
+          <t>-12,94%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 10,02</t>
+          <t>-33,63; 8,85</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 15,23</t>
+          <t>-28,6; 12,35</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-41,48; -0,59</t>
+          <t>-35,7; 7,53</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 25,63</t>
+          <t>-22,32; 26,44</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 26,01</t>
+          <t>-17,72; 32,49</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-43,83; 0,0</t>
+          <t>-33,19; 4,13</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 11,39</t>
+          <t>-19,6; 14,44</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 15,67</t>
+          <t>-18,03; 12,94</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-32,19; -2,0</t>
+          <t>-24,79; 2,47</t>
         </is>
       </c>
     </row>
